--- a/llm_usage_log.xlsx
+++ b/llm_usage_log.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -729,26 +729,229 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
-        <f>"TOTAL calls: "&amp;COUNTA(A2:A10)</f>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-16T10:48:49+00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3385</v>
+      </c>
+      <c r="F11" t="n">
+        <v>333</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-16T10:49:12+00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3964</v>
+      </c>
+      <c r="F12" t="n">
+        <v>255</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-16T10:49:27+00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1819</v>
+      </c>
+      <c r="F13" t="n">
+        <v>236</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-16T10:51:59+00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.101</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F14" t="n">
+        <v>247</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-17T04:52:27+00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.949</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2645</v>
+      </c>
+      <c r="F15" t="n">
+        <v>261</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-17T04:56:23+00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2658</v>
+      </c>
+      <c r="F16" t="n">
+        <v>245</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17T04:58:08+00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2664</v>
+      </c>
+      <c r="F17" t="n">
+        <v>253</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <f>"TOTAL calls: "&amp;COUNTA(A2:A17)</f>
         <v/>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2">
-        <f>SUM(D2:D10)</f>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2">
+        <f>SUM(D2:D17)</f>
         <v/>
       </c>
-      <c r="E11" s="2">
-        <f>SUM(E2:E10)</f>
+      <c r="E18" s="2">
+        <f>SUM(E2:E17)</f>
         <v/>
       </c>
-      <c r="F11" s="2">
-        <f>SUM(F2:F10)</f>
+      <c r="F18" s="2">
+        <f>SUM(F2:F17)</f>
         <v/>
       </c>
-      <c r="G11" s="2">
-        <f>SUM(G2:G10)</f>
+      <c r="G18" s="2">
+        <f>SUM(G2:G17)</f>
         <v/>
       </c>
     </row>

--- a/llm_usage_log.xlsx
+++ b/llm_usage_log.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -932,26 +932,577 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
-        <f>"TOTAL calls: "&amp;COUNTA(A2:A17)</f>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:09:36+00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5029</v>
+      </c>
+      <c r="F18" t="n">
+        <v>212</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:12:00+00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.245</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5034</v>
+      </c>
+      <c r="F19" t="n">
+        <v>226</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:15:18+00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16.997</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2982</v>
+      </c>
+      <c r="F20" t="n">
+        <v>287</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:21:55+00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5034</v>
+      </c>
+      <c r="F21" t="n">
+        <v>239</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:23:55+00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4644</v>
+      </c>
+      <c r="F22" t="n">
+        <v>213</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:33:11+00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3108</v>
+      </c>
+      <c r="F23" t="n">
+        <v>216</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:42:35+00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.554</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2721</v>
+      </c>
+      <c r="F24" t="n">
+        <v>249</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:43:38+00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5029</v>
+      </c>
+      <c r="F25" t="n">
+        <v>207</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:47:16+00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.329</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5034</v>
+      </c>
+      <c r="F26" t="n">
+        <v>261</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:58:38+00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="F27" t="n">
+        <v>258</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:59:04+00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5192</v>
+      </c>
+      <c r="F28" t="n">
+        <v>250</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:01:50+00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4301</v>
+      </c>
+      <c r="F29" t="n">
+        <v>250</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:02:08+00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5315</v>
+      </c>
+      <c r="F30" t="n">
+        <v>229</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:02:11+00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F31" t="n">
+        <v>266</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.169</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4301</v>
+      </c>
+      <c r="F32" t="n">
+        <v>262</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.129</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4930</v>
+      </c>
+      <c r="F33" t="n">
+        <v>250</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:20:36+00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>6.207</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5873</v>
+      </c>
+      <c r="F34" t="n">
+        <v>320</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4.234</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4725</v>
+      </c>
+      <c r="F35" t="n">
+        <v>233</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:56:24+00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3.699</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5470</v>
+      </c>
+      <c r="F36" t="n">
+        <v>216</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <f>"TOTAL calls: "&amp;COUNTA(A2:A36)</f>
         <v/>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2">
-        <f>SUM(D2:D17)</f>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2">
+        <f>SUM(D2:D36)</f>
         <v/>
       </c>
-      <c r="E18" s="2">
-        <f>SUM(E2:E17)</f>
+      <c r="E37" s="2">
+        <f>SUM(E2:E36)</f>
         <v/>
       </c>
-      <c r="F18" s="2">
-        <f>SUM(F2:F17)</f>
+      <c r="F37" s="2">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
-      <c r="G18" s="2">
-        <f>SUM(G2:G17)</f>
+      <c r="G37" s="2">
+        <f>SUM(G2:G36)</f>
         <v/>
       </c>
     </row>
